--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://resbank-my.sharepoint.com/personal/cathy_hlungwani_resbank_co_za/Documents/Documents/1. MEng - Data Science/1. Project_2025/Data/factor_timing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D65831C-1026-46A9-8F8A-D821C0E1019C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{4D65831C-1026-46A9-8F8A-D821C0E1019C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F45BAEAE-48B0-4737-AC24-9D15A9BC772C}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{D77FAABD-B5BB-42C1-A988-BDBEBEA03A87}"/>
+    <workbookView minimized="1" xWindow="2580" yWindow="2580" windowWidth="14400" windowHeight="8170" activeTab="4" xr2:uid="{D77FAABD-B5BB-42C1-A988-BDBEBEA03A87}"/>
   </bookViews>
   <sheets>
     <sheet name="Ecocomic Data" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
     <sheet name="Fundamental Data" sheetId="2" r:id="rId3"/>
     <sheet name="Market Data" sheetId="3" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="380">
   <si>
     <t>SubIndex_PC2</t>
   </si>
@@ -1177,13 +1178,37 @@
   </si>
   <si>
     <t>Allocating  roughly one week to each model.</t>
+  </si>
+  <si>
+    <t>Logistic</t>
+  </si>
+  <si>
+    <t>GAM</t>
+  </si>
+  <si>
+    <t>XGBoost</t>
+  </si>
+  <si>
+    <t>Momentum_vs_benchmark</t>
+  </si>
+  <si>
+    <t>Value_vs_benchmark</t>
+  </si>
+  <si>
+    <t>Quality_vs_benchmark</t>
+  </si>
+  <si>
+    <t>ROC AUC</t>
+  </si>
+  <si>
+    <t>PR AUC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1212,16 +1237,36 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -1346,22 +1391,235 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1375,12 +1633,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1397,18 +1649,63 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEE0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1420,13 +1717,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEE0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1778,7 +2068,7 @@
       <c r="B1" t="s">
         <v>323</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>326</v>
       </c>
     </row>
@@ -1818,10 +2108,10 @@
       <c r="C3" t="s">
         <v>178</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="21" t="s">
         <v>306</v>
       </c>
       <c r="N3" t="s">
@@ -1838,8 +2128,8 @@
       <c r="C4" t="s">
         <v>156</v>
       </c>
-      <c r="L4" s="3"/>
-      <c r="M4" s="2"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="21"/>
       <c r="N4" t="s">
         <v>265</v>
       </c>
@@ -1854,8 +2144,8 @@
       <c r="C5" t="s">
         <v>232</v>
       </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="2"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="21"/>
       <c r="N5" t="s">
         <v>299</v>
       </c>
@@ -1870,8 +2160,8 @@
       <c r="C6" t="s">
         <v>305</v>
       </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="2"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="21"/>
       <c r="N6" t="s">
         <v>261</v>
       </c>
@@ -1886,8 +2176,8 @@
       <c r="C7" t="s">
         <v>172</v>
       </c>
-      <c r="L7" s="3"/>
-      <c r="M7" s="2" t="s">
+      <c r="L7" s="20"/>
+      <c r="M7" s="21" t="s">
         <v>292</v>
       </c>
       <c r="N7" t="s">
@@ -1904,8 +2194,8 @@
       <c r="C8" t="s">
         <v>198</v>
       </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="2"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="21"/>
       <c r="N8" t="s">
         <v>278</v>
       </c>
@@ -1920,8 +2210,8 @@
       <c r="C9" t="s">
         <v>247</v>
       </c>
-      <c r="L9" s="3"/>
-      <c r="M9" s="2"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="21"/>
       <c r="N9" t="s">
         <v>284</v>
       </c>
@@ -1936,10 +2226,10 @@
       <c r="C10" t="s">
         <v>223</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="L10" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="21" t="s">
         <v>279</v>
       </c>
       <c r="N10" t="s">
@@ -1956,8 +2246,8 @@
       <c r="C11" t="s">
         <v>244</v>
       </c>
-      <c r="L11" s="3"/>
-      <c r="M11" s="2"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="21"/>
       <c r="N11" t="s">
         <v>274</v>
       </c>
@@ -1972,8 +2262,8 @@
       <c r="C12" t="s">
         <v>260</v>
       </c>
-      <c r="L12" s="3"/>
-      <c r="M12" s="2"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="21"/>
       <c r="N12" t="s">
         <v>270</v>
       </c>
@@ -1988,8 +2278,8 @@
       <c r="C13" t="s">
         <v>250</v>
       </c>
-      <c r="L13" s="3"/>
-      <c r="M13" s="2" t="s">
+      <c r="L13" s="20"/>
+      <c r="M13" s="21" t="s">
         <v>266</v>
       </c>
       <c r="N13" t="s">
@@ -2006,8 +2296,8 @@
       <c r="C14" t="s">
         <v>235</v>
       </c>
-      <c r="L14" s="3"/>
-      <c r="M14" s="2"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="21"/>
       <c r="N14" t="s">
         <v>261</v>
       </c>
@@ -2022,8 +2312,8 @@
       <c r="C15" t="s">
         <v>290</v>
       </c>
-      <c r="L15" s="3"/>
-      <c r="M15" s="2"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="21"/>
       <c r="N15" t="s">
         <v>257</v>
       </c>
@@ -3138,29 +3428,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="E1" s="5"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:6" ht="15.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="15">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="11">
         <v>45835</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>328</v>
       </c>
       <c r="C3" t="s">
@@ -3171,7 +3461,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>329</v>
       </c>
       <c r="C4" t="s">
@@ -3182,12 +3472,12 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="15">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="11">
         <v>45832</v>
       </c>
       <c r="F5" t="s">
@@ -3195,28 +3485,28 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="22" t="s">
         <v>368</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="23" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="10"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="23"/>
     </row>
     <row r="8" spans="1:6" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="6" t="s">
         <v>369</v>
       </c>
       <c r="C8" t="s">
@@ -3224,17 +3514,17 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="15">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="11">
         <v>45835</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="4" t="s">
         <v>335</v>
       </c>
       <c r="C10" t="s">
@@ -3242,7 +3532,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>336</v>
       </c>
       <c r="C11" t="s">
@@ -3250,26 +3540,26 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="15">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="11">
         <v>45834</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="4" t="s">
         <v>338</v>
       </c>
       <c r="C13" t="s">
         <v>361</v>
       </c>
-      <c r="D13" s="11"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="4" t="s">
         <v>339</v>
       </c>
       <c r="B14" t="s">
@@ -3280,7 +3570,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="4" t="s">
         <v>340</v>
       </c>
       <c r="B15" t="s">
@@ -3291,31 +3581,31 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="4" t="s">
         <v>341</v>
       </c>
       <c r="C16" t="s">
         <v>361</v>
       </c>
-      <c r="D16" s="11"/>
+      <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" ht="15.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="15">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="11">
         <v>45846</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="4" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="5" t="s">
         <v>344</v>
       </c>
       <c r="C19" t="s">
@@ -3323,7 +3613,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="5" t="s">
         <v>345</v>
       </c>
       <c r="C20" t="s">
@@ -3331,7 +3621,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="5" t="s">
         <v>346</v>
       </c>
       <c r="C21" t="s">
@@ -3339,7 +3629,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="5" t="s">
         <v>347</v>
       </c>
       <c r="C22" t="s">
@@ -3347,7 +3637,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="5" t="s">
         <v>348</v>
       </c>
       <c r="C23" t="s">
@@ -3355,17 +3645,17 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="15">
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="11">
         <v>45869</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="4" t="s">
         <v>350</v>
       </c>
       <c r="B25" t="s">
@@ -3376,7 +3666,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="4" t="s">
         <v>351</v>
       </c>
       <c r="B26" t="s">
@@ -3387,7 +3677,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="4" t="s">
         <v>352</v>
       </c>
       <c r="C27" t="s">
@@ -3395,48 +3685,46 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="10"/>
     </row>
     <row r="29" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="4" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="4" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" x14ac:dyDescent="0.35">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="12" t="s">
         <v>356</v>
       </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="14"/>
     </row>
     <row r="32" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="21"/>
+      <c r="D32" s="16"/>
     </row>
     <row r="33" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="22" t="s">
+      <c r="A33" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="B33" s="23" t="s">
+      <c r="B33" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="C33" s="23"/>
-      <c r="D33" s="24"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3447,20 +3735,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{90201749-17A1-4CD9-9288-FD16EED3D638}">
-            <xm:f>NOT(ISERROR(SEARCH($F$3,C3)))</xm:f>
-            <xm:f>$F$3</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFEE0000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>C3:C33</xm:sqref>
-        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="1" operator="containsText" id="{4A8F162F-B450-4EFB-9A15-20B68C730125}">
             <xm:f>NOT(ISERROR(SEARCH($F$5,C3)))</xm:f>
@@ -3486,6 +3760,20 @@
           </x14:cfRule>
           <xm:sqref>C3:C27</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{90201749-17A1-4CD9-9288-FD16EED3D638}">
+            <xm:f>NOT(ISERROR(SEARCH($F$3,C3)))</xm:f>
+            <xm:f>$F$3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFEE0000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>C3:C33</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
@@ -3512,7 +3800,7 @@
       <c r="C1" t="s">
         <v>323</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>325</v>
       </c>
       <c r="F1" s="1"/>
@@ -3555,10 +3843,10 @@
         <v>272</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="21" t="s">
         <v>306</v>
       </c>
       <c r="M3" t="s">
@@ -3576,8 +3864,8 @@
         <v>263</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="2"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="21"/>
       <c r="M4" t="s">
         <v>265</v>
       </c>
@@ -3593,8 +3881,8 @@
         <v>268</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="2"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="21"/>
       <c r="M5" t="s">
         <v>299</v>
       </c>
@@ -3610,8 +3898,8 @@
         <v>231</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="2"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="21"/>
       <c r="M6" t="s">
         <v>261</v>
       </c>
@@ -3627,8 +3915,8 @@
         <v>234</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="2" t="s">
+      <c r="K7" s="20"/>
+      <c r="L7" s="21" t="s">
         <v>292</v>
       </c>
       <c r="M7" t="s">
@@ -3646,8 +3934,8 @@
         <v>228</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="2"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="21"/>
       <c r="M8" t="s">
         <v>278</v>
       </c>
@@ -3660,8 +3948,8 @@
         <v>222</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="2"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="21"/>
       <c r="M9" t="s">
         <v>284</v>
       </c>
@@ -3674,10 +3962,10 @@
         <v>294</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="L10" s="21" t="s">
         <v>279</v>
       </c>
       <c r="M10" t="s">
@@ -3692,8 +3980,8 @@
         <v>255</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="2"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="21"/>
       <c r="M11" t="s">
         <v>274</v>
       </c>
@@ -3703,8 +3991,8 @@
         <v>272</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="2"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="21"/>
       <c r="M12" t="s">
         <v>270</v>
       </c>
@@ -3714,8 +4002,8 @@
         <v>268</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="2" t="s">
+      <c r="K13" s="20"/>
+      <c r="L13" s="21" t="s">
         <v>266</v>
       </c>
       <c r="M13" t="s">
@@ -3727,8 +4015,8 @@
         <v>263</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="2"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="21"/>
       <c r="M14" t="s">
         <v>261</v>
       </c>
@@ -3738,8 +4026,8 @@
         <v>259</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="2"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="21"/>
       <c r="M15" t="s">
         <v>257</v>
       </c>
@@ -5145,7 +5433,7 @@
       <c r="B1" t="s">
         <v>323</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -5179,10 +5467,10 @@
       <c r="C3" t="s">
         <v>289</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="21" t="s">
         <v>306</v>
       </c>
       <c r="I3" t="s">
@@ -5196,8 +5484,8 @@
       <c r="C4" t="s">
         <v>207</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="2"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="21"/>
       <c r="I4" t="s">
         <v>265</v>
       </c>
@@ -5209,8 +5497,8 @@
       <c r="C5" t="s">
         <v>158</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="2"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="21"/>
       <c r="I5" t="s">
         <v>299</v>
       </c>
@@ -5222,8 +5510,8 @@
       <c r="C6" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="2"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="21"/>
       <c r="I6" t="s">
         <v>261</v>
       </c>
@@ -5235,8 +5523,8 @@
       <c r="C7" t="s">
         <v>122</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="2" t="s">
+      <c r="G7" s="20"/>
+      <c r="H7" s="21" t="s">
         <v>292</v>
       </c>
       <c r="I7" t="s">
@@ -5250,8 +5538,8 @@
       <c r="C8" t="s">
         <v>200</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="2"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="21"/>
       <c r="I8" t="s">
         <v>278</v>
       </c>
@@ -5263,8 +5551,8 @@
       <c r="C9" t="s">
         <v>305</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="2"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="21"/>
       <c r="I9" t="s">
         <v>284</v>
       </c>
@@ -5276,10 +5564,10 @@
       <c r="C10" t="s">
         <v>287</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="21" t="s">
         <v>279</v>
       </c>
       <c r="I10" t="s">
@@ -5293,8 +5581,8 @@
       <c r="C11" t="s">
         <v>250</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="2"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="21"/>
       <c r="I11" t="s">
         <v>274</v>
       </c>
@@ -5306,8 +5594,8 @@
       <c r="C12" t="s">
         <v>223</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="2"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="21"/>
       <c r="I12" t="s">
         <v>270</v>
       </c>
@@ -5319,8 +5607,8 @@
       <c r="C13" t="s">
         <v>293</v>
       </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="2" t="s">
+      <c r="G13" s="20"/>
+      <c r="H13" s="21" t="s">
         <v>266</v>
       </c>
       <c r="I13" t="s">
@@ -5338,8 +5626,8 @@
         <f>45+10+15</f>
         <v>70</v>
       </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="2"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="21"/>
       <c r="I14" t="s">
         <v>261</v>
       </c>
@@ -5351,8 +5639,8 @@
       <c r="C15" t="s">
         <v>285</v>
       </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="2"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="21"/>
       <c r="I15" t="s">
         <v>257</v>
       </c>
@@ -6870,6 +7158,89 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95F088C5-84C2-4EFB-835A-3C0825F54802}">
+  <dimension ref="B2:H7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="22.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C3" s="24" t="s">
+        <v>378</v>
+      </c>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="24" t="s">
+        <v>379</v>
+      </c>
+      <c r="G3" s="25"/>
+      <c r="H3" s="26"/>
+    </row>
+    <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C4" s="27" t="s">
+        <v>372</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>373</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>374</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>372</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>373</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B5" s="42" t="s">
+        <v>375</v>
+      </c>
+      <c r="C5" s="40"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="34"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B6" s="43" t="s">
+        <v>376</v>
+      </c>
+      <c r="C6" s="31"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="36"/>
+    </row>
+    <row r="7" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="44" t="s">
+        <v>377</v>
+      </c>
+      <c r="C7" s="41"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="39"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{70c52299-74de-4dfd-b117-c9c408edfa50}" enabled="1" method="Standard" siteId="{853cbaab-a620-4178-8933-88d76414184a}" contentBits="0" removed="0"/>
